--- a/output/isabel-cohorts/김건희반_총점_성장.xlsx
+++ b/output/isabel-cohorts/김건희반_총점_성장.xlsx
@@ -4636,11 +4636,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="36701171"/>
-        <c:axId val="45962695"/>
+        <c:axId val="35722419"/>
+        <c:axId val="58179989"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="36701171"/>
+        <c:axId val="35722419"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4672,7 +4672,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45962695"/>
+        <c:crossAx val="58179989"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4680,7 +4680,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="45962695"/>
+        <c:axId val="58179989"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4724,7 +4724,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36701171"/>
+        <c:crossAx val="35722419"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5182,11 +5182,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="71626810"/>
-        <c:axId val="77567963"/>
+        <c:axId val="29249727"/>
+        <c:axId val="51409147"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="71626810"/>
+        <c:axId val="29249727"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5218,7 +5218,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77567963"/>
+        <c:crossAx val="51409147"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5226,7 +5226,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="77567963"/>
+        <c:axId val="51409147"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5270,7 +5270,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71626810"/>
+        <c:crossAx val="29249727"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6014,11 +6014,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="50461680"/>
-        <c:axId val="51414697"/>
+        <c:axId val="60031951"/>
+        <c:axId val="96215063"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="50461680"/>
+        <c:axId val="60031951"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6050,7 +6050,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51414697"/>
+        <c:crossAx val="96215063"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6058,7 +6058,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="51414697"/>
+        <c:axId val="96215063"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6136,7 +6136,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50461680"/>
+        <c:crossAx val="60031951"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -6436,11 +6436,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="64459604"/>
-        <c:axId val="83106148"/>
+        <c:axId val="29191032"/>
+        <c:axId val="94656059"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="64459604"/>
+        <c:axId val="29191032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6472,7 +6472,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83106148"/>
+        <c:crossAx val="94656059"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6480,7 +6480,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83106148"/>
+        <c:axId val="94656059"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6524,7 +6524,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64459604"/>
+        <c:crossAx val="29191032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7163,11 +7163,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="43735505"/>
-        <c:axId val="58305389"/>
+        <c:axId val="6188901"/>
+        <c:axId val="31134337"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="43735505"/>
+        <c:axId val="6188901"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7199,7 +7199,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58305389"/>
+        <c:crossAx val="31134337"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7207,7 +7207,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="58305389"/>
+        <c:axId val="31134337"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7285,7 +7285,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43735505"/>
+        <c:crossAx val="6188901"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -7585,11 +7585,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="26602575"/>
-        <c:axId val="45559141"/>
+        <c:axId val="57904467"/>
+        <c:axId val="79809996"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="26602575"/>
+        <c:axId val="57904467"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7621,7 +7621,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45559141"/>
+        <c:crossAx val="79809996"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7629,7 +7629,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="45559141"/>
+        <c:axId val="79809996"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7673,7 +7673,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26602575"/>
+        <c:crossAx val="57904467"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8239,11 +8239,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="58535024"/>
-        <c:axId val="36051788"/>
+        <c:axId val="59160848"/>
+        <c:axId val="86969654"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="58535024"/>
+        <c:axId val="59160848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8275,7 +8275,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36051788"/>
+        <c:crossAx val="86969654"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8283,7 +8283,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36051788"/>
+        <c:axId val="86969654"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8361,7 +8361,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58535024"/>
+        <c:crossAx val="59160848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -8661,11 +8661,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="16332294"/>
-        <c:axId val="64798282"/>
+        <c:axId val="26878660"/>
+        <c:axId val="93191784"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="16332294"/>
+        <c:axId val="26878660"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8697,7 +8697,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64798282"/>
+        <c:crossAx val="93191784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8705,7 +8705,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64798282"/>
+        <c:axId val="93191784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8749,7 +8749,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16332294"/>
+        <c:crossAx val="26878660"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/output/isabel-cohorts/김건희반_총점_성장.xlsx
+++ b/output/isabel-cohorts/김건희반_총점_성장.xlsx
@@ -4636,11 +4636,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="35722419"/>
-        <c:axId val="58179989"/>
+        <c:axId val="49091430"/>
+        <c:axId val="64062744"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="35722419"/>
+        <c:axId val="49091430"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4672,7 +4672,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58179989"/>
+        <c:crossAx val="64062744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4680,7 +4680,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="58179989"/>
+        <c:axId val="64062744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4724,7 +4724,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35722419"/>
+        <c:crossAx val="49091430"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5182,11 +5182,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="29249727"/>
-        <c:axId val="51409147"/>
+        <c:axId val="44808792"/>
+        <c:axId val="90770543"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="29249727"/>
+        <c:axId val="44808792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5218,7 +5218,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51409147"/>
+        <c:crossAx val="90770543"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5226,7 +5226,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="51409147"/>
+        <c:axId val="90770543"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5270,7 +5270,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29249727"/>
+        <c:crossAx val="44808792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6014,11 +6014,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="60031951"/>
-        <c:axId val="96215063"/>
+        <c:axId val="74455584"/>
+        <c:axId val="48994547"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="60031951"/>
+        <c:axId val="74455584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6050,7 +6050,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96215063"/>
+        <c:crossAx val="48994547"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6058,7 +6058,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="96215063"/>
+        <c:axId val="48994547"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6136,7 +6136,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60031951"/>
+        <c:crossAx val="74455584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -6436,11 +6436,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="29191032"/>
-        <c:axId val="94656059"/>
+        <c:axId val="54926893"/>
+        <c:axId val="29982529"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="29191032"/>
+        <c:axId val="54926893"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6472,7 +6472,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94656059"/>
+        <c:crossAx val="29982529"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6480,7 +6480,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94656059"/>
+        <c:axId val="29982529"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6524,7 +6524,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29191032"/>
+        <c:crossAx val="54926893"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7163,11 +7163,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="6188901"/>
-        <c:axId val="31134337"/>
+        <c:axId val="97414138"/>
+        <c:axId val="25957187"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="6188901"/>
+        <c:axId val="97414138"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7199,7 +7199,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31134337"/>
+        <c:crossAx val="25957187"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7207,7 +7207,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31134337"/>
+        <c:axId val="25957187"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7285,7 +7285,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6188901"/>
+        <c:crossAx val="97414138"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -7585,11 +7585,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="57904467"/>
-        <c:axId val="79809996"/>
+        <c:axId val="87184377"/>
+        <c:axId val="4153675"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="57904467"/>
+        <c:axId val="87184377"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7621,7 +7621,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79809996"/>
+        <c:crossAx val="4153675"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7629,7 +7629,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="79809996"/>
+        <c:axId val="4153675"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7673,7 +7673,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57904467"/>
+        <c:crossAx val="87184377"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8239,11 +8239,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="59160848"/>
-        <c:axId val="86969654"/>
+        <c:axId val="98908081"/>
+        <c:axId val="46850135"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="59160848"/>
+        <c:axId val="98908081"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8275,7 +8275,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86969654"/>
+        <c:crossAx val="46850135"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8283,7 +8283,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86969654"/>
+        <c:axId val="46850135"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8361,7 +8361,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59160848"/>
+        <c:crossAx val="98908081"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -8661,11 +8661,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="26878660"/>
-        <c:axId val="93191784"/>
+        <c:axId val="34131254"/>
+        <c:axId val="65368050"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="26878660"/>
+        <c:axId val="34131254"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8697,7 +8697,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93191784"/>
+        <c:crossAx val="65368050"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8705,7 +8705,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="93191784"/>
+        <c:axId val="65368050"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8749,7 +8749,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26878660"/>
+        <c:crossAx val="34131254"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/output/isabel-cohorts/김건희반_총점_성장.xlsx
+++ b/output/isabel-cohorts/김건희반_총점_성장.xlsx
@@ -4636,11 +4636,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="49091430"/>
-        <c:axId val="64062744"/>
+        <c:axId val="57142609"/>
+        <c:axId val="24612484"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="49091430"/>
+        <c:axId val="57142609"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4672,7 +4672,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64062744"/>
+        <c:crossAx val="24612484"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4680,7 +4680,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64062744"/>
+        <c:axId val="24612484"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4724,7 +4724,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49091430"/>
+        <c:crossAx val="57142609"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5182,11 +5182,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="44808792"/>
-        <c:axId val="90770543"/>
+        <c:axId val="61799606"/>
+        <c:axId val="17684708"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="44808792"/>
+        <c:axId val="61799606"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5218,7 +5218,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90770543"/>
+        <c:crossAx val="17684708"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5226,7 +5226,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="90770543"/>
+        <c:axId val="17684708"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5270,7 +5270,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44808792"/>
+        <c:crossAx val="61799606"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6014,11 +6014,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="74455584"/>
-        <c:axId val="48994547"/>
+        <c:axId val="30175411"/>
+        <c:axId val="69611161"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="74455584"/>
+        <c:axId val="30175411"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6050,7 +6050,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48994547"/>
+        <c:crossAx val="69611161"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6058,7 +6058,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48994547"/>
+        <c:axId val="69611161"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6136,7 +6136,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74455584"/>
+        <c:crossAx val="30175411"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -6436,11 +6436,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="54926893"/>
-        <c:axId val="29982529"/>
+        <c:axId val="14442490"/>
+        <c:axId val="12384516"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="54926893"/>
+        <c:axId val="14442490"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6472,7 +6472,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29982529"/>
+        <c:crossAx val="12384516"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6480,7 +6480,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29982529"/>
+        <c:axId val="12384516"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6524,7 +6524,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54926893"/>
+        <c:crossAx val="14442490"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7163,11 +7163,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="97414138"/>
-        <c:axId val="25957187"/>
+        <c:axId val="79847309"/>
+        <c:axId val="57595208"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="97414138"/>
+        <c:axId val="79847309"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7199,7 +7199,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25957187"/>
+        <c:crossAx val="57595208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7207,7 +7207,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25957187"/>
+        <c:axId val="57595208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7285,7 +7285,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97414138"/>
+        <c:crossAx val="79847309"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -7585,11 +7585,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="87184377"/>
-        <c:axId val="4153675"/>
+        <c:axId val="12055881"/>
+        <c:axId val="49015053"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="87184377"/>
+        <c:axId val="12055881"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7621,7 +7621,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4153675"/>
+        <c:crossAx val="49015053"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7629,7 +7629,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4153675"/>
+        <c:axId val="49015053"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7673,7 +7673,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87184377"/>
+        <c:crossAx val="12055881"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8239,11 +8239,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="98908081"/>
-        <c:axId val="46850135"/>
+        <c:axId val="63904288"/>
+        <c:axId val="3648430"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="98908081"/>
+        <c:axId val="63904288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8275,7 +8275,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46850135"/>
+        <c:crossAx val="3648430"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8283,7 +8283,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46850135"/>
+        <c:axId val="3648430"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8361,7 +8361,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98908081"/>
+        <c:crossAx val="63904288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -8661,11 +8661,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="34131254"/>
-        <c:axId val="65368050"/>
+        <c:axId val="57453565"/>
+        <c:axId val="43276135"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="34131254"/>
+        <c:axId val="57453565"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8697,7 +8697,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65368050"/>
+        <c:crossAx val="43276135"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8705,7 +8705,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65368050"/>
+        <c:axId val="43276135"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8749,7 +8749,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34131254"/>
+        <c:crossAx val="57453565"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/output/isabel-cohorts/김건희반_총점_성장.xlsx
+++ b/output/isabel-cohorts/김건희반_총점_성장.xlsx
@@ -134,41 +134,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">수능</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">으</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 어려워지는데도</t>
+      <t xml:space="preserve">수능 순서로 어려워지는데도</t>
     </r>
     <r>
       <rPr>
@@ -4636,11 +4602,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="57142609"/>
-        <c:axId val="24612484"/>
+        <c:axId val="31546097"/>
+        <c:axId val="25358707"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="57142609"/>
+        <c:axId val="31546097"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4672,7 +4638,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24612484"/>
+        <c:crossAx val="25358707"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4680,7 +4646,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24612484"/>
+        <c:axId val="25358707"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4724,7 +4690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57142609"/>
+        <c:crossAx val="31546097"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5182,11 +5148,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="61799606"/>
-        <c:axId val="17684708"/>
+        <c:axId val="28417238"/>
+        <c:axId val="87970045"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="61799606"/>
+        <c:axId val="28417238"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5218,7 +5184,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17684708"/>
+        <c:crossAx val="87970045"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5226,7 +5192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="17684708"/>
+        <c:axId val="87970045"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5270,7 +5236,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61799606"/>
+        <c:crossAx val="28417238"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6014,11 +5980,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="30175411"/>
-        <c:axId val="69611161"/>
+        <c:axId val="76637809"/>
+        <c:axId val="59517011"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="30175411"/>
+        <c:axId val="76637809"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6050,7 +6016,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69611161"/>
+        <c:crossAx val="59517011"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6058,7 +6024,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="69611161"/>
+        <c:axId val="59517011"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6136,7 +6102,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30175411"/>
+        <c:crossAx val="76637809"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -6436,11 +6402,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="14442490"/>
-        <c:axId val="12384516"/>
+        <c:axId val="65140394"/>
+        <c:axId val="70178894"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="14442490"/>
+        <c:axId val="65140394"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6472,7 +6438,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12384516"/>
+        <c:crossAx val="70178894"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6480,7 +6446,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12384516"/>
+        <c:axId val="70178894"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6524,7 +6490,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14442490"/>
+        <c:crossAx val="65140394"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7163,11 +7129,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="79847309"/>
-        <c:axId val="57595208"/>
+        <c:axId val="38612303"/>
+        <c:axId val="10835486"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="79847309"/>
+        <c:axId val="38612303"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7199,7 +7165,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57595208"/>
+        <c:crossAx val="10835486"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7207,7 +7173,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="57595208"/>
+        <c:axId val="10835486"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7285,7 +7251,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79847309"/>
+        <c:crossAx val="38612303"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -7585,11 +7551,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="12055881"/>
-        <c:axId val="49015053"/>
+        <c:axId val="3301329"/>
+        <c:axId val="27132951"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="12055881"/>
+        <c:axId val="3301329"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7621,7 +7587,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49015053"/>
+        <c:crossAx val="27132951"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7629,7 +7595,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49015053"/>
+        <c:axId val="27132951"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7673,7 +7639,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12055881"/>
+        <c:crossAx val="3301329"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8239,11 +8205,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="63904288"/>
-        <c:axId val="3648430"/>
+        <c:axId val="61110580"/>
+        <c:axId val="59875593"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="63904288"/>
+        <c:axId val="61110580"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8275,7 +8241,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3648430"/>
+        <c:crossAx val="59875593"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8283,7 +8249,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="3648430"/>
+        <c:axId val="59875593"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8361,7 +8327,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63904288"/>
+        <c:crossAx val="61110580"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -8661,11 +8627,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="57453565"/>
-        <c:axId val="43276135"/>
+        <c:axId val="26157242"/>
+        <c:axId val="76689488"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="57453565"/>
+        <c:axId val="26157242"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8697,7 +8663,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43276135"/>
+        <c:crossAx val="76689488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8705,7 +8671,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43276135"/>
+        <c:axId val="76689488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8749,7 +8715,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57453565"/>
+        <c:crossAx val="26157242"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
